--- a/examples/14_zomato_business/zomato_business_config.xlsx
+++ b/examples/14_zomato_business/zomato_business_config.xlsx
@@ -11,6 +11,10 @@
     <sheet name="target_config" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="sheet_config" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="column_config" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="help_target_config" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="help_sheet_config" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="help_column_config" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="help_data_types" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +32,30 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,8 +70,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -125,6 +154,269 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel parser</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>One setting per row. Only 'setting' and 'value' are read; 'notes' is yours.
+Settings: target, database, db_schema, table_prefix, id_type.
+Credentials (host, user, password) are NEVER read from here - they come from the environment / .env.</t>
+      </text>
+    </comment>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>target (optional)
+Which database to push into.
+  'sqlite'  → a local file (good for testing and small datasets)
+  'postgres' → a PostgreSQL server (production use)
+Example: use 'sqlite' while developing, then switch to 'postgres' for production.
+Allowed: sqlite | postgres (default sqlite)
+Example: postgres</t>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>database (optional)
+SQLite: the file path (e.g. 'loaded.db' creates a file in the working directory).
+PostgreSQL: the database NAME (e.g. 'excel_parser').
+Leave blank to take it from the command line (--database) or the PGDATABASE environment variable.
+Allowed: any path for sqlite; a plain name for postgres
+Example: excel_parser</t>
+      </text>
+    </comment>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <t>db_schema (optional)
+PostgreSQL schema to load into. Created automatically if it does not exist.
+Example: 'staging' puts all tables under the 'staging' schema. Blank = the 'public' schema. Ignored by SQLite (no schemas).
+Allowed: plain name; blank = public. Ignored by SQLite
+Example: staging</t>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="0" shapeId="0">
+      <text>
+        <t>table_prefix (optional)
+A prefix added to every table name.
+Example: if table_prefix='stg_' and table_name='orders', the physical table is 'stg_orders'. Useful for separating staging from production tables in the same schema.
+Blank = no prefix (default).
+Allowed: plain name fragment; blank = no prefix
+Example: (blank)</t>
+      </text>
+    </comment>
+    <comment ref="A6" authorId="0" shapeId="0">
+      <text>
+        <t>id_type (optional)
+How primary keys and file_id are generated.
+  'integer' → auto-incrementing numbers (1, 2, 3...) — simpler, default.
+  'uuid'    → random UUIDs per row — use when merging data from multiple sources where integer IDs would collide.
+Allowed: integer | uuid (default integer)
+Example: integer</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel parser</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>table_name (required)
+The database table name for this block. The physical table becomes &lt;table_prefix&gt;&lt;table_name&gt;.
+Example: if your source has an 'Orders' tab, you might name it 'orders'. Two blocks on the same sheet need different names — e.g. 'card_payments' and 'cash_payments' for two sections on a 'Payments' tab.
+Allowed: lowercase letters, digits, underscore; unique in the workbook; max 63 chars
+Example: orders</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>sheet_name (required)
+The exact tab name in the SOURCE workbook. Must match character for character — copy-paste it from the tab to avoid typos.
+Example: if the tab is called 'Order Level', type exactly 'Order Level'. Excel truncates long tab names (e.g. 'Growth Investments and Other De'), so copy the truncated name.
+Allowed: exact tab name from the source file
+Example: Order Level</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>layout (required)
+Describes the shape of the data block:
+  'table' = a header row (e.g. row 1) followed by data rows below it.
+  'key_value' = labels in one column, values in the next (like a settings block).
+Example: a list of orders with columns Date, Customer, Amount → 'table'. A summary block with 'Total Orders: 42' on one row → 'key_value'.
+Allowed: table | key_value
+Example: table</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>header_row (optional)
+The row number that contains column headers (e.g. 'Date', 'Customer', 'Amount'). Not read as data — only recorded in the audit log.
+Example: if row 1 has headers and data starts at row 2, set header_row=1. Leave blank for key_value layout.
+Allowed: whole number, 1-based as shown in Excel; blank for key_value
+Example: 1</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>data_start_row (required)
+The FIRST row of actual data (not the header, not a title row). Look at the row numbers in Excel.
+Example: if row 1 is headers and data starts at row 2, set data_start_row=2. If there is a title on rows 1–3, headers on row 4, and data from row 5, set data_start_row=5.
+Allowed: whole number, must be below the header/title row
+Example: 2</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>data_end_row (optional)
+The LAST row of data. Set this when there are totals, notes, or another data block below.
+Example: data in rows 2–50, then a 'Grand Total' on row 51 → set data_end_row=50. If another block starts at row 55, fence this one off at row 50.
+Leave blank to read to the last non-empty row in the sheet.
+Allowed: whole number &gt;= data_start_row; blank = read to the last used row
+Example: (blank)</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>active (required)
+Y = this block is processed (table created, data loaded).
+N = completely skipped — use this to park a block you do not want right now without deleting the row.
+Allowed: Y | N
+Example: Y</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>notes (optional)
+Free text for your own use. Copied into the generated SQL as a comment.
+Allowed: any text
+Example: invoice lines, one row per invoice</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>description (optional)
+A human-readable description of what this table contains. Written as a COMMENT ON TABLE in PostgreSQL so BI tools and AI agents can discover meaning.
+Example: 'Order-level payout details from the Swiggy annexure'
+Allowed: any text
+Example: Order-level payout details from the delivery platform</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>domain (optional)
+A business category tag. Prepended to the table comment as [domain].
+Example: 'finance', 'orders', 'inventory', 'hr'
+Allowed: any text
+Example: food_delivery</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel parser</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>table_name (required)
+Which block (from sheet_config) this column belongs to.
+Example: if you defined a block called 'orders' in sheet_config, every column row for that block has table_name='orders'.
+Allowed: must match a table_name on sheet_config
+Example: orders</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>source_ref (required)
+Which Excel column letter to read FROM the source file. The parser reads by column position, NOT by header text.
+Example: if 'Order ID' is in column A → 'col:A'. If 'Amount' is in column D → 'col:D'. Wide sheets: column 30 = 'col:AD'.
+IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all source_ref values when that happens.
+Allowed: col:&lt;letter&gt; (e.g. col:A, col:B, col:AM). No row numbers, no ranges
+Example: col:A</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>source_header (optional)
+The header text as printed in the source file — purely for documentation. The parser never matches by header text; it always uses source_ref.
+Example: if column A has header 'Invoice No', put 'Invoice No' here. This shows up in the ER diagram and preview tooltips. If the supplier renames the header, the load still works — only source_ref matters.
+Allowed: any text; documentation only
+Example: Invoice No</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>column_name (required)
+The database column name to create. Must be unique within the table.
+Example: 'Invoice No' → 'invoice_no', 'Order Date' → 'order_date'.
+Reserved names (added automatically): file_id, sheet_name, source_row_num, &lt;table_name&gt;_id — do not use these.
+Allowed: lowercase letters/digits/underscore, unique within the table, max 63 chars
+Example: invoice_no</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>data_type (required)
+How the cell value is converted. Choose the type based on the MESSIEST value in the column, not just the first row.
+  text     → keeps the text, trims whitespace. Use for names, IDs, mixed content.
+  numeric  → extracts numbers: '₹1,234.50' → 1234.5, '18%' → 18.0
+  integer  → like numeric but truncated: '42.0' → 42
+  date     → converts to YYYY-MM-DD: '02-Aug-2026' → '2026-08-02'
+  timestamp → date + time: '2026-08-02 19:45'
+  boolean  → yes/true/1 → 1, no/false/0 → 0
+If ANY cell can hold '-', 'NA', or a note, use 'text' to avoid NULLs.
+Allowed: text | numeric | integer | date | timestamp | boolean
+Example: text</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>nullable (required)
+Can this column be empty in the source?
+  Y = empty cells are stored as NULL (most columns should use this).
+  N = NOT NULL — any row where this cell is empty is rejected and reported, not loaded.
+Example: 'order_id' should be N (every order must have an ID). 'discount' should be Y (not all orders have a discount).
+When in doubt, use Y — it is safer and you can tighten later.
+Allowed: Y | N
+Example: Y</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>is_key (required)
+Creates a non-unique INDEX on this column for faster lookups. This is NOT a primary key and does NOT deduplicate rows.
+Example: set Y on 'order_id' or 'invoice_no' — columns you will filter or join on. Set N on 'amount', 'description', etc.
+Allowed: Y | N
+Example: N</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>column_order (required)
+Controls the position of this column in the created table. Number them 1, 2, 3... in the order you want.
+Example: invoice_no=1, invoice_date=2, customer=3, amount=4.
+Gaps are fine (1, 5, 10); duplicates make the order arbitrary.
+Allowed: whole number
+Example: 1</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -426,9 +718,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -443,9 +732,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -459,9 +745,6 @@
           <t>Values are mixed numeric: order counts, sales (Rs), percentages, ratings.</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -507,19 +790,24 @@
   </sheetPr>
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>setting</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -612,6 +900,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -623,54 +912,66 @@
   </sheetPr>
   <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>table_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>sheet_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>layout</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>header_row</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>data_start_row</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>data_end_row</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
@@ -721,6 +1022,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -730,51 +1032,57 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>table_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>source_ref</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>source_header</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>column_name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>data_type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>nullable</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>is_key</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>transform</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>column_order</t>
         </is>
@@ -816,12 +1124,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>trim</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
+      <c r="H2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -861,12 +1164,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>trim</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
+      <c r="H3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -906,12 +1204,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>trim</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
+      <c r="H4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -951,12 +1244,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>trim</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="H5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -996,12 +1284,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>trim</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+      <c r="H6" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1041,12 +1324,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>trim</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="H7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1086,12 +1364,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="H8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1131,12 +1404,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="H9" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1176,12 +1444,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="H10" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1221,12 +1484,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="H11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1266,12 +1524,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="H12" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1311,12 +1564,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="H13" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1356,12 +1604,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="H14" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1401,12 +1644,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="H15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1446,12 +1684,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="H16" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1491,12 +1724,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="H17" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1536,12 +1764,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+      <c r="H18" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1581,12 +1804,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="H19" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1626,12 +1844,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="H20" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1671,12 +1884,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+      <c r="H21" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1716,12 +1924,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="H22" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1761,12 +1964,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
+      <c r="H23" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1806,12 +2004,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
+      <c r="H24" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1851,12 +2044,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
+      <c r="H25" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1896,12 +2084,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
+      <c r="H26" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1941,12 +2124,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
+      <c r="H27" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1986,12 +2164,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
+      <c r="H28" t="n">
         <v>27</v>
       </c>
     </row>
@@ -2031,12 +2204,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+      <c r="H29" t="n">
         <v>28</v>
       </c>
     </row>
@@ -2076,12 +2244,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
+      <c r="H30" t="n">
         <v>29</v>
       </c>
     </row>
@@ -2121,12 +2284,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
+      <c r="H31" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2166,12 +2324,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
+      <c r="H32" t="n">
         <v>31</v>
       </c>
     </row>
@@ -2211,12 +2364,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
+      <c r="H33" t="n">
         <v>32</v>
       </c>
     </row>
@@ -2256,12 +2404,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
+      <c r="H34" t="n">
         <v>33</v>
       </c>
     </row>
@@ -2301,12 +2444,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
+      <c r="H35" t="n">
         <v>34</v>
       </c>
     </row>
@@ -2346,12 +2484,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
+      <c r="H36" t="n">
         <v>35</v>
       </c>
     </row>
@@ -2391,14 +2524,1172 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
+      <c r="H37" t="n">
         <v>36</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>target_config - where the rows are pushed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>header / setting</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>what it means</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>allowed values</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Which database to push into.
+  'sqlite'  → a local file (good for testing and small datasets)
+  'postgres' → a PostgreSQL server (production use)
+Example: use 'sqlite' while developing, then switch to 'postgres' for production.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>sqlite | postgres (default sqlite)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>SQLite: the file path (e.g. 'loaded.db' creates a file in the working directory).
+PostgreSQL: the database NAME (e.g. 'excel_parser').
+Leave blank to take it from the command line (--database) or the PGDATABASE environment variable.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>any path for sqlite; a plain name for postgres</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>excel_parser</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>db_schema</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>PostgreSQL schema to load into. Created automatically if it does not exist.
+Example: 'staging' puts all tables under the 'staging' schema. Blank = the 'public' schema. Ignored by SQLite (no schemas).</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>plain name; blank = public. Ignored by SQLite</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>staging</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>table_prefix</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>A prefix added to every table name.
+Example: if table_prefix='stg_' and table_name='orders', the physical table is 'stg_orders'. Useful for separating staging from production tables in the same schema.
+Blank = no prefix (default).</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>plain name fragment; blank = no prefix</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>id_type</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>How primary keys and file_id are generated.
+  'integer' → auto-incrementing numbers (1, 2, 3...) — simpler, default.
+  'uuid'    → random UUIDs per row — use when merging data from multiple sources where integer IDs would collide.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>integer | uuid (default integer)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>sheet_config - one row per block to read</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>header / setting</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>what it means</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>allowed values</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>table_name</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>The database table name for this block. The physical table becomes &lt;table_prefix&gt;&lt;table_name&gt;.
+Example: if your source has an 'Orders' tab, you might name it 'orders'. Two blocks on the same sheet need different names — e.g. 'card_payments' and 'cash_payments' for two sections on a 'Payments' tab.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>lowercase letters, digits, underscore; unique in the workbook; max 63 chars</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>The exact tab name in the SOURCE workbook. Must match character for character — copy-paste it from the tab to avoid typos.
+Example: if the tab is called 'Order Level', type exactly 'Order Level'. Excel truncates long tab names (e.g. 'Growth Investments and Other De'), so copy the truncated name.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>exact tab name from the source file</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Order Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>layout</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Describes the shape of the data block:
+  'table' = a header row (e.g. row 1) followed by data rows below it.
+  'key_value' = labels in one column, values in the next (like a settings block).
+Example: a list of orders with columns Date, Customer, Amount → 'table'. A summary block with 'Total Orders: 42' on one row → 'key_value'.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>table | key_value</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>header_row</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>The row number that contains column headers (e.g. 'Date', 'Customer', 'Amount'). Not read as data — only recorded in the audit log.
+Example: if row 1 has headers and data starts at row 2, set header_row=1. Leave blank for key_value layout.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>whole number, 1-based as shown in Excel; blank for key_value</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>data_start_row</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>The FIRST row of actual data (not the header, not a title row). Look at the row numbers in Excel.
+Example: if row 1 is headers and data starts at row 2, set data_start_row=2. If there is a title on rows 1–3, headers on row 4, and data from row 5, set data_start_row=5.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>whole number, must be below the header/title row</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>data_end_row</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>The LAST row of data. Set this when there are totals, notes, or another data block below.
+Example: data in rows 2–50, then a 'Grand Total' on row 51 → set data_end_row=50. If another block starts at row 55, fence this one off at row 50.
+Leave blank to read to the last non-empty row in the sheet.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>whole number &gt;= data_start_row; blank = read to the last used row</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Y = this block is processed (table created, data loaded).
+N = completely skipped — use this to park a block you do not want right now without deleting the row.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Y | N</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>A human-readable description of what this table contains. Written as a COMMENT ON TABLE in PostgreSQL so BI tools and AI agents can discover meaning.
+Example: 'Order-level payout details from the Swiggy annexure'</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>any text</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Order-level payout details from the delivery platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>A business category tag. Prepended to the table comment as [domain].
+Example: 'finance', 'orders', 'inventory', 'hr'</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>any text</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>food_delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Free text for your own use. Copied into the generated SQL as a comment.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>any text</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>invoice lines, one row per invoice</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>column_config - one row per database column</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>header / setting</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>what it means</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>allowed values</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>table_name</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Which block (from sheet_config) this column belongs to.
+Example: if you defined a block called 'orders' in sheet_config, every column row for that block has table_name='orders'.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>must match a table_name on sheet_config</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>source_ref</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Which Excel column letter to read FROM the source file. The parser reads by column position, NOT by header text.
+Example: if 'Order ID' is in column A → 'col:A'. If 'Amount' is in column D → 'col:D'. Wide sheets: column 30 = 'col:AD'.
+IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all source_ref values when that happens.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>col:&lt;letter&gt; (e.g. col:A, col:B, col:AM). No row numbers, no ranges</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>col:A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>source_header</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>The header text as printed in the source file — purely for documentation. The parser never matches by header text; it always uses source_ref.
+Example: if column A has header 'Invoice No', put 'Invoice No' here. This shows up in the ER diagram and preview tooltips. If the supplier renames the header, the load still works — only source_ref matters.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>any text; documentation only</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Invoice No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>column_name</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>The database column name to create. Must be unique within the table.
+Example: 'Invoice No' → 'invoice_no', 'Order Date' → 'order_date'.
+Reserved names (added automatically): file_id, sheet_name, source_row_num, &lt;table_name&gt;_id — do not use these.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>lowercase letters/digits/underscore, unique within the table, max 63 chars</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>invoice_no</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>data_type</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>How the cell value is converted. Choose the type based on the MESSIEST value in the column, not just the first row.
+  text     → keeps the text, trims whitespace. Use for names, IDs, mixed content.
+  numeric  → extracts numbers: '₹1,234.50' → 1234.5, '18%' → 18.0
+  integer  → like numeric but truncated: '42.0' → 42
+  date     → converts to YYYY-MM-DD: '02-Aug-2026' → '2026-08-02'
+  timestamp → date + time: '2026-08-02 19:45'
+  boolean  → yes/true/1 → 1, no/false/0 → 0
+If ANY cell can hold '-', 'NA', or a note, use 'text' to avoid NULLs.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>text | numeric | integer | date | timestamp | boolean</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>nullable</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Can this column be empty in the source?
+  Y = empty cells are stored as NULL (most columns should use this).
+  N = NOT NULL — any row where this cell is empty is rejected and reported, not loaded.
+Example: 'order_id' should be N (every order must have an ID). 'discount' should be Y (not all orders have a discount).
+When in doubt, use Y — it is safer and you can tighten later.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Y | N</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>is_key</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Creates a non-unique INDEX on this column for faster lookups. This is NOT a primary key and does NOT deduplicate rows.
+Example: set Y on 'order_id' or 'invoice_no' — columns you will filter or join on. Set N on 'amount', 'description', etc.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Y | N</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>column_order</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Controls the position of this column in the created table. Number them 1, 2, 3... in the order you want.
+Example: invoice_no=1, invoice_date=2, customer=3, amount=4.
+Gaps are fine (1, 5, 10); duplicates make the order arbitrary.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>whole number</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Transformations applied AFTER type casting on every cell value. Chain multiple with | (pipe).
+TEXT examples:
+  trim             '  hello  ' → 'hello'
+  uppercase        'hello' → 'HELLO'
+  lowercase        'HELLO' → 'hello'
+  titlecase        'hello world' → 'Hello World'
+  digits_only      'INV-001' → '001'
+  letters_only     'Order-123' → 'Order'
+  alphanum_only    'Order #123!' → 'Order123'
+  collapse_spaces  'hello    world' → 'hello world'
+  replace_newlines 'line1\nline2' → 'line1 line2'
+  remove_punctuation 'Hello, World!' → 'Hello World'
+  first_word       'John Smith' → 'John'
+  last_word        'John Smith' → 'Smith'
+  left_10 / right_10  first/last 10 characters
+  slug             'Hello World!' → 'hello-world'
+NUMERIC examples:
+  abs              -120.5 → 120.5
+  negate           100 → -100
+  round_2          3.14159 → 3.14
+  round_1          3.456 → 3.5
+  round_0          3.7 → 4.0
+  floor / ceil     3.9 → 3 / 3.1 → 4
+  pct_to_fraction  18.0 → 0.18
+  fraction_to_pct  0.18 → 18.0
+  clamp_0          -5 → 0 (negatives become 0)
+DATE examples:
+  date_only        '2026-08-02T19:45' → '2026-08-02'
+  year_month       '2026-08-02' → '2026-08'
+  year_only        '2026-08-02' → '2026'
+GUARD:
+  not_null         error if NULL
+  not_empty        error if NULL or empty string</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>chain with |, e.g. trim|uppercase</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>trim</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>What this column represents. Written as a COMMENT ON COLUMN in PostgreSQL so BI tools and AI agents can understand the schema.
+Example: 'Unique order identifier assigned by the platform'</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>any text</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Unique order identifier from the platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Unit of measurement for numeric columns. Appended to the column comment.
+Example: 'INR' for Indian Rupees, 'USD', 'percent', 'count', 'kg'</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>any text</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>null_default</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>What to store when a cell is empty, instead of NULL.
+Examples:
+  numeric/integer column: '0' → stores 0 instead of NULL
+  text column: 'N/A' or '' → stores that string instead of NULL
+  boolean column: '0' or 'false' → stores 0 instead of NULL
+Applied after type casting, so a cell with '-' that casts to NULL also gets the default. Leave blank to keep NULL (the default behavior).</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>any value appropriate for the data_type; blank = store NULL</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>references</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Declares a foreign-key relationship to another table's column. Shown as a dashed line in the ER diagram. Does NOT create a database constraint — it is for documentation and the diagram only.
+Example: if this column references the 'order_id' column in the 'orders' table, write 'orders.order_id'. The ER diagram will draw an arrow from this column to orders.order_id.</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>table_name.column_name (must reference an existing table and column)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>orders.order_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>data_type - what the loader does to the cell value</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>data_type</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>conversion</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>trimmed; an empty cell becomes NULL</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>" VISA "  -&gt;  VISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>keeps digits, . and -; a bracketed value becomes negative</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>₹1,234.50 -&gt; 1234.5   18% -&gt; 18.0   (₹120.00) -&gt; -120.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>as numeric, then cut to a whole number</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>"42.0"  -&gt;  42</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Excel dates and common text dates -&gt; YYYY-MM-DD; '-' and 'NA' -&gt; NULL; anything else -&gt; NULL and reported</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>02-08-2026  -&gt;  2026-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>as date, keeping the time</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02 19:45  -&gt;  2026-08-02T19:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>y/yes/true/1 -&gt; 1, n/no/false/0 -&gt; 0, anything else NULL</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Yes  -&gt;  1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>A value that does not fit its type is stored as NULL and listed at the end of the load - fix the data_type when you see that.</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/14_zomato_business/zomato_business_config.xlsx
+++ b/examples/14_zomato_business/zomato_business_config.xlsx
@@ -343,10 +343,30 @@
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>source_ref (required)
-Which Excel column letter to read FROM the source file. The parser reads by column position, NOT by header text.
-Example: if 'Order ID' is in column A → 'col:A'. If 'Amount' is in column D → 'col:D'. Wide sheets: column 30 = 'col:AD'.
-IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all source_ref values when that happens.
-Allowed: col:&lt;letter&gt; (e.g. col:A, col:B, col:AM). No row numbers, no ranges
+Where to get the value for this column. Four formats:
+1. Column reference: 'col:&lt;letter&gt;' — reads from the source file by position, NOT by header text. Example: col:A, col:D, col:AM.
+2. Constant value: 'const:&lt;value&gt;' — fills every row with a fixed value. Example: const:adarsh, const:100.
+3. Computed value: 'fn:&lt;name&gt;' — fills every row with a value computed at load time. Available functions:
+  fn:now       — current timestamp (timestamp, text)
+  fn:today     — current date (date, text)
+  fn:uuid      — random UUID per row (text)
+  fn:file_name — source file name (text)
+  fn:sequence  — counter 1,2,3... per table (integer, numeric, text)
+4. Expression: 'expr:&lt;expression&gt;' — computes a value from other columns, constants, functions and literals. Use {X} to reference Excel column X.
+  Operators: + - * / (numeric), &amp; (string concatenation)
+  Grouping: parentheses ( ) to override precedence
+  Unary minus: -{A} to negate a value
+  NULL handling: arithmetic with NULL -&gt; NULL (like SQL)
+  Examples:
+    expr:{D} + {E}             (sum two columns)
+    expr:({A} + {B}) * {C}     (grouped arithmetic)
+    expr:-{D}                  (negate a value)
+    expr:{A} &amp; " - " &amp; {C}    (concatenate with separator)
+    expr:{D} * 0.18            (calculate 18% tax)
+All results are cast to the column's data_type. 'script' and
+'null_default' apply after the expression result is cast.
+IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all col: and expr: source_ref values when that happens.
+Allowed: col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, or expr:&lt;expression&gt;
 Example: col:A</t>
       </text>
     </comment>
@@ -2740,7 +2760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2958,109 +2978,146 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>row_filter</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Skip rows that don't match this condition.
+Use col:LETTER to reference a cell (same as source_ref), then an operator and a value.
+Operators:
+  =  !=  &gt;  &lt;  &gt;=  &lt;=        compare text or numbers
+  contains  not_contains     text search inside the cell
+  is_empty  is_not_empty     check for blank cells (no value needed)
+Examples:
+  col:A is_not_empty              skip blank rows
+  col:D &gt; 0                       only positive amounts
+  col:B = "Delivered"             only delivered orders
+  col:C != "Cancelled"            exclude cancelled
+  col:E contains "swiggy"         cell contains the word
+  col:D &gt; 100 AND col:F != "NA"   combine two conditions
+  col:A = "Active" OR col:A = "Pending"   either status
+Leave blank to load all rows (default).</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>col:LETTER op value [AND/OR ...]; blank = all rows</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
           <t>active</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Y = this block is processed (table created, data loaded).
 N = completely skipped — use this to park a block you do not want right now without deleting the row.</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Y | N</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>A human-readable description of what this table contains. Written as a COMMENT ON TABLE in PostgreSQL so BI tools and AI agents can discover meaning.
 Example: 'Order-level payout details from the Swiggy annexure'</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>any text</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Order-level payout details from the delivery platform</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>A business category tag. Prepended to the table comment as [domain].
 Example: 'finance', 'orders', 'inventory', 'hr'</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>any text</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>food_delivery</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Free text for your own use. Copied into the generated SQL as a comment.</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>any text</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>invoice lines, one row per invoice</t>
         </is>
@@ -3077,7 +3134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3162,14 +3219,34 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Which Excel column letter to read FROM the source file. The parser reads by column position, NOT by header text.
-Example: if 'Order ID' is in column A → 'col:A'. If 'Amount' is in column D → 'col:D'. Wide sheets: column 30 = 'col:AD'.
-IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all source_ref values when that happens.</t>
+          <t>Where to get the value for this column. Four formats:
+1. Column reference: 'col:&lt;letter&gt;' — reads from the source file by position, NOT by header text. Example: col:A, col:D, col:AM.
+2. Constant value: 'const:&lt;value&gt;' — fills every row with a fixed value. Example: const:adarsh, const:100.
+3. Computed value: 'fn:&lt;name&gt;' — fills every row with a value computed at load time. Available functions:
+  fn:now       — current timestamp (timestamp, text)
+  fn:today     — current date (date, text)
+  fn:uuid      — random UUID per row (text)
+  fn:file_name — source file name (text)
+  fn:sequence  — counter 1,2,3... per table (integer, numeric, text)
+4. Expression: 'expr:&lt;expression&gt;' — computes a value from other columns, constants, functions and literals. Use {X} to reference Excel column X.
+  Operators: + - * / (numeric), &amp; (string concatenation)
+  Grouping: parentheses ( ) to override precedence
+  Unary minus: -{A} to negate a value
+  NULL handling: arithmetic with NULL -&gt; NULL (like SQL)
+  Examples:
+    expr:{D} + {E}             (sum two columns)
+    expr:({A} + {B}) * {C}     (grouped arithmetic)
+    expr:-{D}                  (negate a value)
+    expr:{A} &amp; " - " &amp; {C}    (concatenate with separator)
+    expr:{D} * 0.18            (calculate 18% tax)
+All results are cast to the column's data_type. 'script' and
+'null_default' apply after the expression result is cast.
+IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all col: and expr: source_ref values when that happens.</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>col:&lt;letter&gt; (e.g. col:A, col:B, col:AM). No row numbers, no ranges</t>
+          <t>col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, or expr:&lt;expression&gt;</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -3532,6 +3609,36 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>date_format</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Pin the date parsing to a specific format instead of auto-detecting.
+Without this, the parser tries multiple formats in order — which means '01/02/2026' could be January 2 or February 1 depending on which format matches first.
+Set this to eliminate ambiguity:
+  %d/%m/%Y   → DD/MM/YYYY (European/Indian: 01/02/2026 = Feb 1)
+  %m/%d/%Y   → MM/DD/YYYY (American: 01/02/2026 = Jan 2)
+  %Y-%m-%d   → YYYY-MM-DD (ISO)
+  %d-%b-%Y   → DD-Mon-YYYY (02-Aug-2026)
+Only applies to date and timestamp columns. Ignored for other types.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Python strptime format string; blank = auto-detect</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/examples/14_zomato_business/zomato_business_config.xlsx
+++ b/examples/14_zomato_business/zomato_business_config.xlsx
@@ -363,10 +363,14 @@
     expr:-{D}                  (negate a value)
     expr:{A} &amp; " - " &amp; {C}    (concatenate with separator)
     expr:{D} * 0.18            (calculate 18% tax)
+5. Positional map: 'map:v1||v2||v3||...' — assigns a different value to each row by position. The first data row gets v1, the second gets v2, and so on. Use || (double pipe) to separate values.
+  Example: map:Name||Area||City||ID||GSTIN
+  Ideal for key_value blocks where the source has no label column.
+  If the map has fewer values than rows, extra rows get NULL.
 All results are cast to the column's data_type. 'script' and
 'null_default' apply after the expression result is cast.
 IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all col: and expr: source_ref values when that happens.
-Allowed: col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, or expr:&lt;expression&gt;
+Allowed: col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, expr:&lt;expression&gt;, or map:v1||v2||...
 Example: col:A</t>
       </text>
     </comment>
@@ -3239,6 +3243,10 @@
     expr:-{D}                  (negate a value)
     expr:{A} &amp; " - " &amp; {C}    (concatenate with separator)
     expr:{D} * 0.18            (calculate 18% tax)
+5. Positional map: 'map:v1||v2||v3||...' — assigns a different value to each row by position. The first data row gets v1, the second gets v2, and so on. Use || (double pipe) to separate values.
+  Example: map:Name||Area||City||ID||GSTIN
+  Ideal for key_value blocks where the source has no label column.
+  If the map has fewer values than rows, extra rows get NULL.
 All results are cast to the column's data_type. 'script' and
 'null_default' apply after the expression result is cast.
 IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all col: and expr: source_ref values when that happens.</t>
@@ -3246,7 +3254,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, or expr:&lt;expression&gt;</t>
+          <t>col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, expr:&lt;expression&gt;, or map:v1||v2||...</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
